--- a/.00_resource/EduStayAI Roadmap.xlsx
+++ b/.00_resource/EduStayAI Roadmap.xlsx
@@ -9,13 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Milestones" sheetId="4" r:id="rId2"/>
-    <sheet name="Notes" sheetId="3" r:id="rId3"/>
-    <sheet name="temp" sheetId="2" r:id="rId4"/>
+    <sheet name="Requirements" sheetId="5" r:id="rId3"/>
+    <sheet name="Notes" sheetId="3" r:id="rId4"/>
+    <sheet name="temp" sheetId="2" r:id="rId5"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="471">
   <si>
     <t>Roadmap Phát Triển Sản Phẩm &amp; Marketing (1 Người + AI)</t>
   </si>
@@ -651,13 +652,840 @@
   </si>
   <si>
     <t>T01-11/2028</t>
+  </si>
+  <si>
+    <t>1. User</t>
+  </si>
+  <si>
+    <t>Ví dụ:</t>
+  </si>
+  <si>
+    <t>Tháng 6/2026 launch app</t>
+  </si>
+  <si>
+    <t>Có 1.000 người đăng ký</t>
+  </si>
+  <si>
+    <t>=&gt; KPI User = 1.000</t>
+  </si>
+  <si>
+    <t>Tuy nhiên chỉ số này dễ "ảo".</t>
+  </si>
+  <si>
+    <t>1.000 người đăng ký</t>
+  </si>
+  <si>
+    <t>Chỉ 10 người còn dùng</t>
+  </si>
+  <si>
+    <t>=&gt; App vẫn thất bại.</t>
+  </si>
+  <si>
+    <t>2. DAU (Daily Active Users)</t>
+  </si>
+  <si>
+    <t>Là số người thực sự sử dụng app mỗi ngày.</t>
+  </si>
+  <si>
+    <t>Ngày</t>
+  </si>
+  <si>
+    <t>User mở app</t>
+  </si>
+  <si>
+    <t>Thứ 2</t>
+  </si>
+  <si>
+    <t>Thứ 3</t>
+  </si>
+  <si>
+    <t>Thứ 4</t>
+  </si>
+  <si>
+    <t>Thứ 5</t>
+  </si>
+  <si>
+    <t>=&gt; DAU trung bình khoảng 110.</t>
+  </si>
+  <si>
+    <t>Đối với app học tập mới:</t>
+  </si>
+  <si>
+    <t>DAU 100 là khá ổn</t>
+  </si>
+  <si>
+    <t>DAU 500 là tốt</t>
+  </si>
+  <si>
+    <t>DAU 1.000+ là rất tốt</t>
+  </si>
+  <si>
+    <t>3. D7 Retention</t>
+  </si>
+  <si>
+    <t>Đây là KPI quan trọng nhất.</t>
+  </si>
+  <si>
+    <t>Cách tính:</t>
+  </si>
+  <si>
+    <t>Ví dụ ngày 1 có:</t>
+  </si>
+  <si>
+    <t>100 người đăng ký</t>
+  </si>
+  <si>
+    <t>Sau 7 ngày:</t>
+  </si>
+  <si>
+    <t>25 người vẫn quay lại học</t>
+  </si>
+  <si>
+    <t>=&gt; D7 = 25%</t>
+  </si>
+  <si>
+    <t>Công thức:</t>
+  </si>
+  <si>
+    <t>D7 Retention=User quay lại ngaˋy thứ 7User đa˘ng kyˊ ban đa^ˋu×100%D7\ Retention = \frac{User\ quay\ lại\ ngày\ thứ\ 7}{User\ đăng\ ký\ ban\ đầu} \times 100\%D7 Retention=User đa˘ng kyˊ​ ban đa^ˋuUser quay lại ngaˋy thứ 7​×100%</t>
+  </si>
+  <si>
+    <t>D7 bao nhiêu là tốt?</t>
+  </si>
+  <si>
+    <t>D7</t>
+  </si>
+  <si>
+    <t>Đánh giá</t>
+  </si>
+  <si>
+    <t>&lt;10%</t>
+  </si>
+  <si>
+    <t>Rất tệ</t>
+  </si>
+  <si>
+    <t>10-20%</t>
+  </si>
+  <si>
+    <t>Trung bình</t>
+  </si>
+  <si>
+    <t>20-30%</t>
+  </si>
+  <si>
+    <t>Tốt</t>
+  </si>
+  <si>
+    <t>30-40%</t>
+  </si>
+  <si>
+    <t>Rất tốt</t>
+  </si>
+  <si>
+    <t>&gt;40%</t>
+  </si>
+  <si>
+    <t>Xuất sắc</t>
+  </si>
+  <si>
+    <t>Đối với app học tiếng Anh mới:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mục tiêu ban đầu: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>20%</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sau khi tối ưu: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>25-30%</t>
+    </r>
+  </si>
+  <si>
+    <t>Ví dụ thực tế cho app của bạn</t>
+  </si>
+  <si>
+    <t>Giả sử sau 3 tháng:</t>
+  </si>
+  <si>
+    <t>DAU = 120</t>
+  </si>
+  <si>
+    <t>D7 = 25%</t>
+  </si>
+  <si>
+    <t>=&gt; Đây là tín hiệu khá tốt.</t>
+  </si>
+  <si>
+    <t>Tiếp tục 6 tháng:</t>
+  </si>
+  <si>
+    <t>5.000 user</t>
+  </si>
+  <si>
+    <t>DAU = 500</t>
+  </si>
+  <si>
+    <t>D7 = 30%</t>
+  </si>
+  <si>
+    <t>=&gt; Lúc này có thể bắt đầu mở Premium.</t>
+  </si>
+  <si>
+    <t>Nếu chỉ được chọn 1 KPI để theo dõi</t>
+  </si>
+  <si>
+    <t>Thì hãy theo:</t>
+  </si>
+  <si>
+    <t>D7 Retention</t>
+  </si>
+  <si>
+    <t>Vì:</t>
+  </si>
+  <si>
+    <t>User có thể mua quảng cáo được.</t>
+  </si>
+  <si>
+    <t>Download có thể mua được.</t>
+  </si>
+  <si>
+    <t>Nhưng nếu người dùng không quay lại học thì app không có giá trị.</t>
+  </si>
+  <si>
+    <t>Đối với app học tiếng Anh của bạn, tôi sẽ ưu tiên KPI theo thứ tự:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. D7 Retention</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (quan trọng nhất)</t>
+    </r>
+  </si>
+  <si>
+    <t>2. DAU</t>
+  </si>
+  <si>
+    <t>3. Số phút học trung bình/ngày</t>
+  </si>
+  <si>
+    <t>4. Tỷ lệ hoàn thành bài học</t>
+  </si>
+  <si>
+    <t>5. Tổng số user đăng ký</t>
+  </si>
+  <si>
+    <t>Đó là bộ KPI mà các app như Duolingo hay ELSA Speak cũng rất quan tâm trong giai đoạn đầu tăng trưởng.</t>
+  </si>
+  <si>
+    <t>Edu-Stay AI - Product Backlog &amp; Roadmap</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>Feature / Requirement</t>
+  </si>
+  <si>
+    <t>User Value</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Effort</t>
+  </si>
+  <si>
+    <t>Release</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Dependency</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>UI-001</t>
+  </si>
+  <si>
+    <t>UX/UI</t>
+  </si>
+  <si>
+    <t>Refactor toàn bộ UI theo hướng mobile-first</t>
+  </si>
+  <si>
+    <t>Tăng usability</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>MVP</t>
+  </si>
+  <si>
+    <t>Todo</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>Mobile là kênh sử dụng chính</t>
+  </si>
+  <si>
+    <t>UI-002</t>
+  </si>
+  <si>
+    <t>Giảm scroll, tối ưu "vùng đất vàng"</t>
+  </si>
+  <si>
+    <t>Tăng engagement</t>
+  </si>
+  <si>
+    <t>Ưu tiên thông tin quan trọng ở first screen</t>
+  </si>
+  <si>
+    <t>UI-003</t>
+  </si>
+  <si>
+    <t>Tách Dashboard và Lesson thành 2 page riêng</t>
+  </si>
+  <si>
+    <t>Điều hướng rõ ràng</t>
+  </si>
+  <si>
+    <t>Navigation đơn giản hơn</t>
+  </si>
+  <si>
+    <t>UI-004</t>
+  </si>
+  <si>
+    <t>Tăng độ tương phản text trên mobile</t>
+  </si>
+  <si>
+    <t>Cải thiện khả năng đọc</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Fix button, radio, option text</t>
+  </si>
+  <si>
+    <t>UI-005</t>
+  </si>
+  <si>
+    <t>Thu nhỏ logo show, avatar user</t>
+  </si>
+  <si>
+    <t>Tối ưu không gian</t>
+  </si>
+  <si>
+    <t>Giảm kích thước 30-50%</t>
+  </si>
+  <si>
+    <t>UI-006</t>
+  </si>
+  <si>
+    <t>Thiết kế lại left menu</t>
+  </si>
+  <si>
+    <t>Gọn gàng hơn</t>
+  </si>
+  <si>
+    <t>Bỏ thông tin test</t>
+  </si>
+  <si>
+    <t>UI-007</t>
+  </si>
+  <si>
+    <t>Rút gọn wording cho Gen Z</t>
+  </si>
+  <si>
+    <t>Dễ sử dụng</t>
+  </si>
+  <si>
+    <t>Hạn chế text dài</t>
+  </si>
+  <si>
+    <t>UI-008</t>
+  </si>
+  <si>
+    <t>Architecture</t>
+  </si>
+  <si>
+    <t>Tách code UI thành modules</t>
+  </si>
+  <si>
+    <t>Dễ maintain</t>
+  </si>
+  <si>
+    <t>Tránh file &gt;500 dòng</t>
+  </si>
+  <si>
+    <t>POD-001</t>
+  </si>
+  <si>
+    <t>Podcast Learning</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách podcast show từ DB sau login</t>
+  </si>
+  <si>
+    <t>Giảm thao tác nhập link</t>
+  </si>
+  <si>
+    <t>DB Shows</t>
+  </si>
+  <si>
+    <t>Mặc định hiển thị sẵn</t>
+  </si>
+  <si>
+    <t>POD-002</t>
+  </si>
+  <si>
+    <t>Cho phép nhập RSS/URL nếu show chưa có</t>
+  </si>
+  <si>
+    <t>Mở rộng nội dung</t>
+  </si>
+  <si>
+    <t>Fallback</t>
+  </si>
+  <si>
+    <t>POD-003</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách episodes của show</t>
+  </si>
+  <si>
+    <t>Chọn bài học dễ dàng</t>
+  </si>
+  <si>
+    <t>Episode browser</t>
+  </si>
+  <si>
+    <t>POD-004</t>
+  </si>
+  <si>
+    <t>Embedded audio player</t>
+  </si>
+  <si>
+    <t>Trải nghiệm học</t>
+  </si>
+  <si>
+    <t>Core feature</t>
+  </si>
+  <si>
+    <t>POD-005</t>
+  </si>
+  <si>
+    <t>Transcript đồng bộ audio</t>
+  </si>
+  <si>
+    <t>Tăng khả năng nghe hiểu</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Sentence level sync</t>
+  </si>
+  <si>
+    <t>POD-006</t>
+  </si>
+  <si>
+    <t>Highlight transcript theo audio time</t>
+  </si>
+  <si>
+    <t>Theo dõi dễ dàng</t>
+  </si>
+  <si>
+    <t>Karaoke style</t>
+  </si>
+  <si>
+    <t>POD-007</t>
+  </si>
+  <si>
+    <t>Click transcript để jump audio</t>
+  </si>
+  <si>
+    <t>Học nhanh</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>PMF</t>
+  </si>
+  <si>
+    <t>Optional</t>
+  </si>
+  <si>
+    <t>ANA-001</t>
+  </si>
+  <si>
+    <t>Analytics</t>
+  </si>
+  <si>
+    <t>Lưu lịch sử học</t>
+  </si>
+  <si>
+    <t>Tracking tiến độ</t>
+  </si>
+  <si>
+    <t>User Profile</t>
+  </si>
+  <si>
+    <t>ANA-002</t>
+  </si>
+  <si>
+    <t>Dashboard học tập</t>
+  </si>
+  <si>
+    <t>Theo dõi kết quả</t>
+  </si>
+  <si>
+    <t>ANA-003</t>
+  </si>
+  <si>
+    <t>Learning Progress</t>
+  </si>
+  <si>
+    <t>Tạo động lực</t>
+  </si>
+  <si>
+    <t>ANA-004</t>
+  </si>
+  <si>
+    <t>Streak Tracking</t>
+  </si>
+  <si>
+    <t>Retention</t>
+  </si>
+  <si>
+    <t>ANA-005</t>
+  </si>
+  <si>
+    <t>Daily Challenge</t>
+  </si>
+  <si>
+    <t>Engagement</t>
+  </si>
+  <si>
+    <t>ANA-006</t>
+  </si>
+  <si>
+    <t>Leaderboard</t>
+  </si>
+  <si>
+    <t>Gamification</t>
+  </si>
+  <si>
+    <t>AI-001</t>
+  </si>
+  <si>
+    <t>AI Coach</t>
+  </si>
+  <si>
+    <t>AI Pronunciation Scoring</t>
+  </si>
+  <si>
+    <t>Speaking improvement</t>
+  </si>
+  <si>
+    <t>Speaking Engine</t>
+  </si>
+  <si>
+    <t>AI-002</t>
+  </si>
+  <si>
+    <t>AI Conversation</t>
+  </si>
+  <si>
+    <t>Speaking practice</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>XL</t>
+  </si>
+  <si>
+    <t>AI Infra</t>
+  </si>
+  <si>
+    <t>AI-003</t>
+  </si>
+  <si>
+    <t>Roleplay Mode</t>
+  </si>
+  <si>
+    <t>Interactive learning</t>
+  </si>
+  <si>
+    <t>AI-004</t>
+  </si>
+  <si>
+    <t>Writing Correction</t>
+  </si>
+  <si>
+    <t>Writing skill</t>
+  </si>
+  <si>
+    <t>AI-005</t>
+  </si>
+  <si>
+    <t>Reading Quiz</t>
+  </si>
+  <si>
+    <t>Reading skill</t>
+  </si>
+  <si>
+    <t>Content Engine</t>
+  </si>
+  <si>
+    <t>MON-001</t>
+  </si>
+  <si>
+    <t>Monetization</t>
+  </si>
+  <si>
+    <t>Premium AI Speaking</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>MON-002</t>
+  </si>
+  <si>
+    <t>Premium Writing Feedback</t>
+  </si>
+  <si>
+    <t>MON-003</t>
+  </si>
+  <si>
+    <t>Advanced Analytics</t>
+  </si>
+  <si>
+    <t>MON-004</t>
+  </si>
+  <si>
+    <t>Podcast System</t>
+  </si>
+  <si>
+    <t>IELTS-001</t>
+  </si>
+  <si>
+    <t>IELTS Listening</t>
+  </si>
+  <si>
+    <t>Exam prep</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>Existing Listening</t>
+  </si>
+  <si>
+    <t>IELTS-002</t>
+  </si>
+  <si>
+    <t>IELTS Reading</t>
+  </si>
+  <si>
+    <t>Quiz Engine</t>
+  </si>
+  <si>
+    <t>IELTS-003</t>
+  </si>
+  <si>
+    <t>IELTS Writing</t>
+  </si>
+  <si>
+    <t>AI Writing</t>
+  </si>
+  <si>
+    <t>IELTS-004</t>
+  </si>
+  <si>
+    <t>IELTS Speaking</t>
+  </si>
+  <si>
+    <t>AI Speaking</t>
+  </si>
+  <si>
+    <t>IELTS-005</t>
+  </si>
+  <si>
+    <t>AI Examiner</t>
+  </si>
+  <si>
+    <t>Simulation</t>
+  </si>
+  <si>
+    <t>IELTS Modules</t>
+  </si>
+  <si>
+    <t>B2B-001</t>
+  </si>
+  <si>
+    <t>B2B Education</t>
+  </si>
+  <si>
+    <t>Teacher management</t>
+  </si>
+  <si>
+    <t>P5</t>
+  </si>
+  <si>
+    <t>B2B-002</t>
+  </si>
+  <si>
+    <t>User Management</t>
+  </si>
+  <si>
+    <t>B2B-003</t>
+  </si>
+  <si>
+    <t>Báo cáo tiến độ học viên</t>
+  </si>
+  <si>
+    <t>Teacher insights</t>
+  </si>
+  <si>
+    <t>HSK-001</t>
+  </si>
+  <si>
+    <t>Listening</t>
+  </si>
+  <si>
+    <t>Chinese learning</t>
+  </si>
+  <si>
+    <t>P6</t>
+  </si>
+  <si>
+    <t>English Framework</t>
+  </si>
+  <si>
+    <t>HSK-002</t>
+  </si>
+  <si>
+    <t>Speaking</t>
+  </si>
+  <si>
+    <t>HSK-003</t>
+  </si>
+  <si>
+    <t>Reading</t>
+  </si>
+  <si>
+    <t>HSK-004</t>
+  </si>
+  <si>
+    <t>Writing</t>
+  </si>
+  <si>
+    <t>EDU-001</t>
+  </si>
+  <si>
+    <t>K12 Education</t>
+  </si>
+  <si>
+    <t>Toán lớp 8</t>
+  </si>
+  <si>
+    <t>K12 market</t>
+  </si>
+  <si>
+    <t>P8</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Learning Platform</t>
+  </si>
+  <si>
+    <t>EDU-002</t>
+  </si>
+  <si>
+    <t>KHTN lớp 8</t>
+  </si>
+  <si>
+    <t>EDU-003</t>
+  </si>
+  <si>
+    <t>Tiếng Anh SGK</t>
+  </si>
+  <si>
+    <t>EDU-004</t>
+  </si>
+  <si>
+    <t>AI Tutor</t>
+  </si>
+  <si>
+    <t>EDU-005</t>
+  </si>
+  <si>
+    <t>Quiz System</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>New</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -684,6 +1512,14 @@
     <font>
       <b/>
       <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -716,7 +1552,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -766,6 +1602,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1932,7 +2771,1581 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:L50"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="31" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>282</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>285</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>288</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>289</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>290</v>
+      </c>
+      <c r="L3" s="13" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B4" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J4" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="K4" s="16" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B5" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="E5" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="F5" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H5" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I5" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J5" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B6" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>307</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H6" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B7" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>310</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="H7" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I7" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J7" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="K7" s="16" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B8" s="16" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="H8" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="K8" s="16" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="16" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>320</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J9" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="K9" s="16" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B10" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>324</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="H10" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I10" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J10" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="K10" s="16" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B11" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="E11" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="F11" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H11" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="K11" s="16" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B12" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H12" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I12" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J12" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="K12" s="16" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B13" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D13" s="16" t="s">
+        <v>338</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>339</v>
+      </c>
+      <c r="F13" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="H13" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I13" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J13" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="K13" s="16" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B14" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J14" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="K14" s="16" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B15" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>346</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>347</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H15" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I15" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J15" s="16" t="s">
+        <v>341</v>
+      </c>
+      <c r="K15" s="16" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B16" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>350</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H16" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="K16" s="16" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B17" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>355</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>356</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H17" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I17" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J17" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="K17" s="16" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B18" s="16" t="s">
+        <v>358</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>332</v>
+      </c>
+      <c r="D18" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H18" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I18" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J18" s="16" t="s">
+        <v>354</v>
+      </c>
+      <c r="K18" s="16" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B19" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D19" s="16" t="s">
+        <v>366</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>367</v>
+      </c>
+      <c r="F19" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H19" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="I19" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J19" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B20" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>370</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>371</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I20" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J20" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B21" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D21" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="F21" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I21" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J21" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="K21" s="16"/>
+    </row>
+    <row r="22" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B22" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>377</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H22" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I22" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J22" s="16" t="s">
+        <v>364</v>
+      </c>
+      <c r="K22" s="16"/>
+    </row>
+    <row r="23" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="16" t="s">
+        <v>378</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>380</v>
+      </c>
+      <c r="F23" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H23" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I23" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J23" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="K23" s="16"/>
+    </row>
+    <row r="24" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="16" t="s">
+        <v>381</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H24" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I24" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J24" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="K24" s="16"/>
+    </row>
+    <row r="25" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B25" s="16" t="s">
+        <v>384</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H25" s="16" t="s">
+        <v>362</v>
+      </c>
+      <c r="I25" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J25" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="K25" s="16"/>
+    </row>
+    <row r="26" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B26" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H26" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="I26" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J26" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="K26" s="16"/>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B27" s="16" t="s">
+        <v>395</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="E27" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H27" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="I27" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J27" s="16" t="s">
+        <v>389</v>
+      </c>
+      <c r="K27" s="16"/>
+    </row>
+    <row r="28" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B28" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>400</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H28" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="I28" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J28" s="16" t="s">
+        <v>394</v>
+      </c>
+      <c r="K28" s="16"/>
+    </row>
+    <row r="29" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B29" s="16" t="s">
+        <v>401</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H29" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="I29" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J29" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="K29" s="16"/>
+    </row>
+    <row r="30" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B30" s="16" t="s">
+        <v>405</v>
+      </c>
+      <c r="C30" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>407</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H30" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I30" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J30" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B31" s="16" t="s">
+        <v>410</v>
+      </c>
+      <c r="C31" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="F31" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H31" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I31" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J31" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B32" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>413</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H32" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I32" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J32" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B33" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="H33" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="I33" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J33" s="16" t="s">
+        <v>415</v>
+      </c>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B34" s="16" t="s">
+        <v>416</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J34" s="16" t="s">
+        <v>420</v>
+      </c>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B35" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H35" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I35" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J35" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B36" s="16" t="s">
+        <v>424</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>425</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H36" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>426</v>
+      </c>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B37" s="16" t="s">
+        <v>427</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D37" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H37" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I37" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J37" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B38" s="16" t="s">
+        <v>430</v>
+      </c>
+      <c r="C38" s="16" t="s">
+        <v>102</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>431</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>419</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H38" s="16" t="s">
+        <v>196</v>
+      </c>
+      <c r="I38" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J38" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B39" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="C39" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J39" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B40" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="C40" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>436</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H40" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="I40" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J40" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B41" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="C41" s="16" t="s">
+        <v>435</v>
+      </c>
+      <c r="D41" s="16" t="s">
+        <v>441</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>442</v>
+      </c>
+      <c r="F41" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H41" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="I41" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J41" s="16" t="s">
+        <v>365</v>
+      </c>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B42" s="16" t="s">
+        <v>443</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H42" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J42" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B43" s="16" t="s">
+        <v>448</v>
+      </c>
+      <c r="C43" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43" s="16" t="s">
+        <v>449</v>
+      </c>
+      <c r="E43" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="F43" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H43" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I43" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J43" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B44" s="16" t="s">
+        <v>450</v>
+      </c>
+      <c r="C44" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H44" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I44" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J44" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B45" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="C45" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="16" t="s">
+        <v>453</v>
+      </c>
+      <c r="E45" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="F45" s="16" t="s">
+        <v>446</v>
+      </c>
+      <c r="G45" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="H45" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="I45" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J45" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B46" s="16" t="s">
+        <v>454</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>456</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="F46" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="G46" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H46" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="I46" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J46" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B47" s="16" t="s">
+        <v>461</v>
+      </c>
+      <c r="C47" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="D47" s="16" t="s">
+        <v>462</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="F47" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="G47" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H47" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="I47" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J47" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B48" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="C48" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="D48" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="E48" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="F48" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="G48" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H48" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="I48" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J48" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="49" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B49" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="C49" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="D49" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="E49" s="16" t="s">
+        <v>457</v>
+      </c>
+      <c r="F49" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="G49" s="16" t="s">
+        <v>393</v>
+      </c>
+      <c r="H49" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="I49" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J49" s="16" t="s">
+        <v>385</v>
+      </c>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="50" spans="2:12" x14ac:dyDescent="0.35">
+      <c r="B50" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>455</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="F50" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="G50" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="H50" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="I50" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="J50" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.1796875" style="14" bestFit="1" customWidth="1"/>
@@ -1985,12 +4398,654 @@
         <v>151</v>
       </c>
     </row>
+    <row r="6" spans="1:3" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B6" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="C6"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B7"/>
+      <c r="C7"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C8"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B9" s="6"/>
+      <c r="C9"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B10" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C10"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B11" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B12"/>
+      <c r="C12"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B13" t="s">
+        <v>212</v>
+      </c>
+      <c r="C13"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B14"/>
+      <c r="C14"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B15" t="s">
+        <v>213</v>
+      </c>
+      <c r="C15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B16"/>
+      <c r="C16"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B17" t="s">
+        <v>209</v>
+      </c>
+      <c r="C17"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B18" s="6"/>
+      <c r="C18"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B19" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B20" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B21"/>
+      <c r="C21"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C22"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B23"/>
+      <c r="C23"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B24"/>
+      <c r="C24"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B25"/>
+      <c r="C25"/>
+    </row>
+    <row r="26" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B26" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="C26"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B27"/>
+      <c r="C27"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B28" t="s">
+        <v>218</v>
+      </c>
+      <c r="C28"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B29"/>
+      <c r="C29"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B30" t="s">
+        <v>209</v>
+      </c>
+      <c r="C30"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B31"/>
+      <c r="C31"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B32" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="C33" s="3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B34" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C34" s="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B35" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="C35" s="3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B36" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C36" s="3">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B37"/>
+      <c r="C37"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B38" t="s">
+        <v>225</v>
+      </c>
+      <c r="C38"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B39"/>
+      <c r="C39"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B40" t="s">
+        <v>226</v>
+      </c>
+      <c r="C40"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B41" s="6"/>
+      <c r="C41"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B42" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C42"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B43" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C43"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B44" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="C44"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B45"/>
+      <c r="C45"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B46"/>
+      <c r="C46"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B47"/>
+      <c r="C47"/>
+    </row>
+    <row r="48" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B48" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B49"/>
+      <c r="C49"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B50" t="s">
+        <v>231</v>
+      </c>
+      <c r="C50"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B51"/>
+      <c r="C51"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
+        <v>232</v>
+      </c>
+      <c r="C52"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B53"/>
+      <c r="C53"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B54" t="s">
+        <v>233</v>
+      </c>
+      <c r="C54"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B55" s="6"/>
+      <c r="C55"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B56" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="C56"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B57"/>
+      <c r="C57"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B58" t="s">
+        <v>235</v>
+      </c>
+      <c r="C58"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B59" s="6"/>
+      <c r="C59"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B60" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="C60"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B61"/>
+      <c r="C61"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B62" t="s">
+        <v>237</v>
+      </c>
+      <c r="C62"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B63"/>
+      <c r="C63"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B64" t="s">
+        <v>238</v>
+      </c>
+      <c r="C64"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B65"/>
+      <c r="C65"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B66" t="s">
+        <v>239</v>
+      </c>
+      <c r="C66"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B67"/>
+      <c r="C67"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B68"/>
+      <c r="C68"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B69"/>
+      <c r="C69"/>
+    </row>
+    <row r="70" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B70" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C70"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B71"/>
+      <c r="C71"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B72" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B73" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B74" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B75" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B76" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B77" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B78"/>
+      <c r="C78"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B79" t="s">
+        <v>253</v>
+      </c>
+      <c r="C79"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B80" s="6"/>
+      <c r="C80"/>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B81" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="C81"/>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B82" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C82"/>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B83"/>
+      <c r="C83"/>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B84"/>
+      <c r="C84"/>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B85"/>
+      <c r="C85"/>
+    </row>
+    <row r="86" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B86" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C86"/>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B87"/>
+      <c r="C87"/>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B88" t="s">
+        <v>257</v>
+      </c>
+      <c r="C88"/>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B89" s="6"/>
+      <c r="C89"/>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B90" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C90"/>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B91" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C91"/>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B92" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="C92"/>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B93"/>
+      <c r="C93"/>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B94" t="s">
+        <v>260</v>
+      </c>
+      <c r="C94"/>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B95"/>
+      <c r="C95"/>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B96" t="s">
+        <v>261</v>
+      </c>
+      <c r="C96"/>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B97" s="6"/>
+      <c r="C97"/>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B98" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="C98"/>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B99" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C99"/>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B100" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="C100"/>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B101"/>
+      <c r="C101"/>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B102" t="s">
+        <v>265</v>
+      </c>
+      <c r="C102"/>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B103"/>
+      <c r="C103"/>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B104"/>
+      <c r="C104"/>
+    </row>
+    <row r="105" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B105"/>
+      <c r="C105"/>
+    </row>
+    <row r="106" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B106" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="C106"/>
+    </row>
+    <row r="107" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B107"/>
+      <c r="C107"/>
+    </row>
+    <row r="108" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B108" t="s">
+        <v>267</v>
+      </c>
+      <c r="C108"/>
+    </row>
+    <row r="109" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B109"/>
+      <c r="C109"/>
+    </row>
+    <row r="110" spans="2:3" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="B110" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C110"/>
+    </row>
+    <row r="111" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B111"/>
+      <c r="C111"/>
+    </row>
+    <row r="112" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B112" t="s">
+        <v>269</v>
+      </c>
+      <c r="C112"/>
+    </row>
+    <row r="113" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B113" s="6"/>
+      <c r="C113"/>
+    </row>
+    <row r="114" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B114" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C114"/>
+    </row>
+    <row r="115" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B115" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C115"/>
+    </row>
+    <row r="116" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B116" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="C116"/>
+    </row>
+    <row r="117" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B117"/>
+      <c r="C117"/>
+    </row>
+    <row r="118" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B118" t="s">
+        <v>273</v>
+      </c>
+      <c r="C118"/>
+    </row>
+    <row r="119" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B119" s="6"/>
+      <c r="C119"/>
+    </row>
+    <row r="120" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B120" s="9" t="s">
+        <v>274</v>
+      </c>
+      <c r="C120"/>
+    </row>
+    <row r="121" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B121" s="9" t="s">
+        <v>275</v>
+      </c>
+      <c r="C121"/>
+    </row>
+    <row r="122" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B122" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C122"/>
+    </row>
+    <row r="123" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B123" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="C123"/>
+    </row>
+    <row r="124" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B124" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C124"/>
+    </row>
+    <row r="125" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B125"/>
+      <c r="C125"/>
+    </row>
+    <row r="126" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B126" t="s">
+        <v>279</v>
+      </c>
+      <c r="C126"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/.00_resource/EduStayAI Roadmap.xlsx
+++ b/.00_resource/EduStayAI Roadmap.xlsx
@@ -9,14 +9,16 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7310" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Plan" sheetId="1" r:id="rId1"/>
     <sheet name="Milestones" sheetId="4" r:id="rId2"/>
     <sheet name="Requirements" sheetId="5" r:id="rId3"/>
-    <sheet name="Notes" sheetId="3" r:id="rId4"/>
-    <sheet name="temp" sheetId="2" r:id="rId5"/>
+    <sheet name="Requirements (2)" sheetId="6" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="7" r:id="rId5"/>
+    <sheet name="Notes" sheetId="3" r:id="rId6"/>
+    <sheet name="temp" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="471">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2019" uniqueCount="725">
   <si>
     <t>Roadmap Phát Triển Sản Phẩm &amp; Marketing (1 Người + AI)</t>
   </si>
@@ -360,88 +362,28 @@
     <t>thay vì mở nhiều mảng cùng lúc. Điều này giúp giảm rủi ro, có doanh thu sớm và tận dụng lại 80-90% hệ thống AI, bài học và hạ tầng đã xây dựng.</t>
   </si>
   <si>
-    <t>Thời gian tương đối</t>
-  </si>
-  <si>
-    <t>Hoàn thiện Listening + Podcast + Speaking. Fix bug, tối ưu UX/UI, onboarding.</t>
-  </si>
-  <si>
-    <t>Soft launch, mời tester, thu thập feedback.</t>
-  </si>
-  <si>
-    <t>100-300 user</t>
-  </si>
-  <si>
     <t>06/2026 - 08/2026</t>
   </si>
   <si>
-    <t>Streak, Daily Challenge, Leaderboard, Learning Progress, AI Pronunciation Scoring.</t>
-  </si>
-  <si>
-    <t>TikTok 3-5 video/ngày, Facebook Group, YouTube Shorts, Referral.</t>
-  </si>
-  <si>
     <t>09/2026 - 11/2026</t>
   </si>
   <si>
-    <t>Podcast, TED, News, AI Conversation, Roleplay, Reading Quiz, Writing Correction.</t>
-  </si>
-  <si>
-    <t>SEO, content marketing, xây cộng đồng Facebook/Discord.</t>
-  </si>
-  <si>
     <t>12/2026 - 02/2027</t>
   </si>
   <si>
-    <t>Premium Features, AI Speaking, Writing Feedback, Learning Analytics.</t>
-  </si>
-  <si>
-    <t>Remarketing, Referral Premium, Email Marketing.</t>
-  </si>
-  <si>
-    <t>49k-99k/tháng</t>
-  </si>
-  <si>
     <t>12/2026 - 05/2027</t>
   </si>
   <si>
-    <t>Content IELTS, hợp tác giáo viên IELTS, KOL nhỏ.</t>
-  </si>
-  <si>
     <t>06/2027 - 08/2027</t>
   </si>
   <si>
-    <t>Dashboard giáo viên, quản lý lớp học, báo cáo học tập.</t>
-  </si>
-  <si>
-    <t>Tiếp cận trung tâm tiếng Anh, giáo viên.</t>
-  </si>
-  <si>
     <t>06/2027 - 11/2027</t>
   </si>
   <si>
-    <t>HSK1, HSK2, HSK3 (Listening, Speaking, Reading, Writing).</t>
-  </si>
-  <si>
-    <t>TikTok tiếng Trung, cộng đồng HSK.</t>
-  </si>
-  <si>
     <t>12/2027 - 05/2028</t>
   </si>
   <si>
-    <t>HSK4-6 nếu HSK1-3 thành công.</t>
-  </si>
-  <si>
-    <t>Mở rộng cộng đồng học tiếng Trung.</t>
-  </si>
-  <si>
     <t>12/2027 - 11/2028</t>
-  </si>
-  <si>
-    <t>Toán 8, KHTN 8, Tiếng Anh 8, AI Tutor, Video, Quiz.</t>
-  </si>
-  <si>
-    <t>Hợp tác giáo viên, phụ huynh, trường học.</t>
   </si>
   <si>
     <t>Timeline</t>
@@ -1479,6 +1421,874 @@
   </si>
   <si>
     <t>New</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Những requirement mới này thực ra rất giá trị vì chúng giúp Edu-Stay AI chuyển từ một ứng dụng luyện nghe thành một </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>AI English Coach hoàn chỉnh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Mình đề xuất bổ sung thành các Epic mới như sau:</t>
+  </si>
+  <si>
+    <t>Feature</t>
+  </si>
+  <si>
+    <t>POD-008</t>
+  </si>
+  <si>
+    <t>Podcast Intelligence</t>
+  </si>
+  <si>
+    <t>Podcast Difficulty Assessment</t>
+  </si>
+  <si>
+    <t>Đánh giá độ khó từng podcast</t>
+  </si>
+  <si>
+    <t>POD-009</t>
+  </si>
+  <si>
+    <t>CEFR Level Detection (A1-C2)</t>
+  </si>
+  <si>
+    <t>Người học chọn đúng trình độ</t>
+  </si>
+  <si>
+    <t>POD-010</t>
+  </si>
+  <si>
+    <t>Vocabulary Extraction</t>
+  </si>
+  <si>
+    <t>Tự động lấy từ vựng quan trọng từ transcript</t>
+  </si>
+  <si>
+    <t>POD-011</t>
+  </si>
+  <si>
+    <t>Smart Flashcard Generator</t>
+  </si>
+  <si>
+    <t>Tạo flashcard từ podcast</t>
+  </si>
+  <si>
+    <t>POD-012</t>
+  </si>
+  <si>
+    <t>Personalized Vocabulary List</t>
+  </si>
+  <si>
+    <t>Cá nhân hóa từ vựng theo learner</t>
+  </si>
+  <si>
+    <t>Learner Assessment &amp; Learning Path</t>
+  </si>
+  <si>
+    <t>ASM-001</t>
+  </si>
+  <si>
+    <t>English Placement Test</t>
+  </si>
+  <si>
+    <t>Kiểm tra trình độ đầu vào</t>
+  </si>
+  <si>
+    <t>ASM-002</t>
+  </si>
+  <si>
+    <t>Listening Assessment</t>
+  </si>
+  <si>
+    <t>Đánh giá kỹ năng nghe</t>
+  </si>
+  <si>
+    <t>ASM-003</t>
+  </si>
+  <si>
+    <t>Speaking Assessment</t>
+  </si>
+  <si>
+    <t>Đánh giá kỹ năng nói</t>
+  </si>
+  <si>
+    <t>ASM-004</t>
+  </si>
+  <si>
+    <t>Vocabulary Assessment</t>
+  </si>
+  <si>
+    <t>Đánh giá vốn từ vựng</t>
+  </si>
+  <si>
+    <t>ASM-005</t>
+  </si>
+  <si>
+    <t>CEFR Score Estimation</t>
+  </si>
+  <si>
+    <t>Ước lượng A1-A2-B1-B2-C1-C2</t>
+  </si>
+  <si>
+    <t>AI Learning Path</t>
+  </si>
+  <si>
+    <t>PATH-001</t>
+  </si>
+  <si>
+    <t>Personalized Learning Roadmap</t>
+  </si>
+  <si>
+    <t>Có lộ trình rõ ràng</t>
+  </si>
+  <si>
+    <t>PATH-002</t>
+  </si>
+  <si>
+    <t>Weekly Learning Plan</t>
+  </si>
+  <si>
+    <t>Biết học gì mỗi tuần</t>
+  </si>
+  <si>
+    <t>PATH-003</t>
+  </si>
+  <si>
+    <t>Adaptive Difficulty Engine</t>
+  </si>
+  <si>
+    <t>Nội dung tự tăng giảm độ khó</t>
+  </si>
+  <si>
+    <t>PATH-004</t>
+  </si>
+  <si>
+    <t>AI Study Recommendations</t>
+  </si>
+  <si>
+    <t>Đề xuất bài học tiếp theo</t>
+  </si>
+  <si>
+    <t>GAME-001</t>
+  </si>
+  <si>
+    <t>Learning Streak</t>
+  </si>
+  <si>
+    <t>Tăng retention</t>
+  </si>
+  <si>
+    <t>GAME-002</t>
+  </si>
+  <si>
+    <t>XP System</t>
+  </si>
+  <si>
+    <t>Tạo động lực học</t>
+  </si>
+  <si>
+    <t>GAME-003</t>
+  </si>
+  <si>
+    <t>Achievement Badges</t>
+  </si>
+  <si>
+    <t>Khuyến khích hoàn thành</t>
+  </si>
+  <si>
+    <t>GAME-004</t>
+  </si>
+  <si>
+    <t>Progress Milestones</t>
+  </si>
+  <si>
+    <t>Theo dõi tiến bộ</t>
+  </si>
+  <si>
+    <t>GAME-005</t>
+  </si>
+  <si>
+    <t>Global Leaderboard</t>
+  </si>
+  <si>
+    <t>Tạo cạnh tranh</t>
+  </si>
+  <si>
+    <t>GAME-006</t>
+  </si>
+  <si>
+    <t>Friend Leaderboard</t>
+  </si>
+  <si>
+    <t>Học cùng bạn bè</t>
+  </si>
+  <si>
+    <t>AI Speaking Coach</t>
+  </si>
+  <si>
+    <t>AI-006</t>
+  </si>
+  <si>
+    <t>AI Role-play Mode</t>
+  </si>
+  <si>
+    <t>Hội thoại thực tế</t>
+  </si>
+  <si>
+    <t>AI-007</t>
+  </si>
+  <si>
+    <t>Daily Speaking Scenarios</t>
+  </si>
+  <si>
+    <t>Tình huống hàng ngày</t>
+  </si>
+  <si>
+    <t>AI-008</t>
+  </si>
+  <si>
+    <t>Business English Scenarios</t>
+  </si>
+  <si>
+    <t>Giao tiếp công việc</t>
+  </si>
+  <si>
+    <t>AI-009</t>
+  </si>
+  <si>
+    <t>Travel Scenarios</t>
+  </si>
+  <si>
+    <t>Giao tiếp du lịch</t>
+  </si>
+  <si>
+    <t>Pronunciation Coach</t>
+  </si>
+  <si>
+    <t>PRO-001</t>
+  </si>
+  <si>
+    <t>Pronunciation</t>
+  </si>
+  <si>
+    <t>Chấm điểm phát âm</t>
+  </si>
+  <si>
+    <t>PRO-002</t>
+  </si>
+  <si>
+    <t>Word-level Analysis</t>
+  </si>
+  <si>
+    <t>Sai từ nào biết từ đó</t>
+  </si>
+  <si>
+    <t>PRO-003</t>
+  </si>
+  <si>
+    <t>Phoneme Analysis</t>
+  </si>
+  <si>
+    <t>Sai âm nào biết âm đó</t>
+  </si>
+  <si>
+    <t>PRO-004</t>
+  </si>
+  <si>
+    <t>Visual Pronunciation Feedback</t>
+  </si>
+  <si>
+    <t>Feedback trực quan</t>
+  </si>
+  <si>
+    <t>PRO-005</t>
+  </si>
+  <si>
+    <t>Pronunciation Improvement Plan</t>
+  </si>
+  <si>
+    <t>Kế hoạch cải thiện phát âm</t>
+  </si>
+  <si>
+    <t>Vocabulary System</t>
+  </si>
+  <si>
+    <t>VOC-001</t>
+  </si>
+  <si>
+    <t>Vocabulary</t>
+  </si>
+  <si>
+    <t>Vocabulary Builder</t>
+  </si>
+  <si>
+    <t>Hệ thống học từ vựng</t>
+  </si>
+  <si>
+    <t>VOC-002</t>
+  </si>
+  <si>
+    <t>Spaced Repetition (SRS)</t>
+  </si>
+  <si>
+    <t>Nhớ từ lâu dài</t>
+  </si>
+  <si>
+    <t>VOC-003</t>
+  </si>
+  <si>
+    <t>AI Vocabulary Review</t>
+  </si>
+  <si>
+    <t>Ôn tập thông minh</t>
+  </si>
+  <si>
+    <t>VOC-004</t>
+  </si>
+  <si>
+    <t>Vocabulary Mastery Tracking</t>
+  </si>
+  <si>
+    <t>Theo dõi vốn từ</t>
+  </si>
+  <si>
+    <t>Offline Learning</t>
+  </si>
+  <si>
+    <t>OFF-001</t>
+  </si>
+  <si>
+    <t>Offline Mode</t>
+  </si>
+  <si>
+    <t>Download Podcast</t>
+  </si>
+  <si>
+    <t>Học không cần mạng</t>
+  </si>
+  <si>
+    <t>OFF-002</t>
+  </si>
+  <si>
+    <t>Offline Transcript</t>
+  </si>
+  <si>
+    <t>Đọc transcript offline</t>
+  </si>
+  <si>
+    <t>OFF-003</t>
+  </si>
+  <si>
+    <t>Offline Vocabulary Review</t>
+  </si>
+  <si>
+    <t>Ôn từ vựng offline</t>
+  </si>
+  <si>
+    <t>OFF-004</t>
+  </si>
+  <si>
+    <t>Sync Learning Progress</t>
+  </si>
+  <si>
+    <t>Đồng bộ khi online</t>
+  </si>
+  <si>
+    <t>Sau khi bổ sung, mình đề xuất điều chỉnh roadmap</t>
+  </si>
+  <si>
+    <t>P0 - MVP Launch (Tháng 6-7/2026)</t>
+  </si>
+  <si>
+    <t>UI Refactor</t>
+  </si>
+  <si>
+    <t>Mobile Optimization</t>
+  </si>
+  <si>
+    <t>Podcast Show Browser</t>
+  </si>
+  <si>
+    <t>Episode Browser</t>
+  </si>
+  <si>
+    <t>Embedded Audio</t>
+  </si>
+  <si>
+    <t>Transcript Viewer</t>
+  </si>
+  <si>
+    <t>Transcript Highlight</t>
+  </si>
+  <si>
+    <t>Learning History</t>
+  </si>
+  <si>
+    <t>P1 - Product Market Fit (08-10/2026)</t>
+  </si>
+  <si>
+    <t>Placement Test</t>
+  </si>
+  <si>
+    <t>Learning Path Generator</t>
+  </si>
+  <si>
+    <t>Streak</t>
+  </si>
+  <si>
+    <t>XP</t>
+  </si>
+  <si>
+    <t>Progress Tracking</t>
+  </si>
+  <si>
+    <t>Smart Flashcards</t>
+  </si>
+  <si>
+    <t>P2 - AI English Coach (11/2026 - 02/2027)</t>
+  </si>
+  <si>
+    <t>AI Roleplay</t>
+  </si>
+  <si>
+    <t>SRS</t>
+  </si>
+  <si>
+    <t>Adaptive Learning</t>
+  </si>
+  <si>
+    <t>Pronunciation Analysis</t>
+  </si>
+  <si>
+    <t>P3 - Freemium (03-05/2027)</t>
+  </si>
+  <si>
+    <t>Premium Analytics</t>
+  </si>
+  <si>
+    <t>Premium Speaking</t>
+  </si>
+  <si>
+    <t>Premium Writing</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Nếu xét theo tác động tới tăng trưởng người dùng và khả năng một người + AI triển khai được, thì </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4 feature đáng làm ngay sau MVP</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là:</t>
+    </r>
+  </si>
+  <si>
+    <t>1. Placement Test</t>
+  </si>
+  <si>
+    <t>2. Learning Path Generator</t>
+  </si>
+  <si>
+    <t>3. Smart Flashcards từ Podcast</t>
+  </si>
+  <si>
+    <t>4. Transcript Highlight Sync</t>
+  </si>
+  <si>
+    <t>Đây là các tính năng tạo khác biệt rõ rệt so với các app luyện nghe thông thường mà vẫn có chi phí phát triển hợp lý.</t>
+  </si>
+  <si>
+    <t>Edu-Stay AI - Product Requirement Backlog</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>UI/UX</t>
+  </si>
+  <si>
+    <t>Refactor toàn bộ UI theo hướng Mobile First</t>
+  </si>
+  <si>
+    <t>Tăng trải nghiệm mobile</t>
+  </si>
+  <si>
+    <t>Tối ưu không gian hiển thị, giảm scroll, tận dụng vùng đất vàng</t>
+  </si>
+  <si>
+    <t>Fix text bị mờ trên mobile (button, option, radio, selectbox...)</t>
+  </si>
+  <si>
+    <t>Tăng khả năng đọc</t>
+  </si>
+  <si>
+    <t>Thu nhỏ logo show, avatar user và các hình ảnh không cần thiết</t>
+  </si>
+  <si>
+    <t>Tiết kiệm không gian</t>
+  </si>
+  <si>
+    <t>Thiết kế UI ưu tiên tốc độ, ít thao tác, nhất quán</t>
+  </si>
+  <si>
+    <t>Tăng UX</t>
+  </si>
+  <si>
+    <t>Đưa các hành động chính vào vùng dễ nhìn, dễ truy cập</t>
+  </si>
+  <si>
+    <t>Tăng conversion</t>
+  </si>
+  <si>
+    <t>Thiết kế lại Left Menu gọn gàng, thanh thoát</t>
+  </si>
+  <si>
+    <t>UI-009</t>
+  </si>
+  <si>
+    <t>Loại bỏ thông tin test/debug khỏi giao diện</t>
+  </si>
+  <si>
+    <t>Giao diện chuyên nghiệp</t>
+  </si>
+  <si>
+    <t>UI-010</t>
+  </si>
+  <si>
+    <t>Rút gọn wording theo phong cách Gen Z</t>
+  </si>
+  <si>
+    <t>ARC-001</t>
+  </si>
+  <si>
+    <t>Tách code UI thành modules riêng</t>
+  </si>
+  <si>
+    <t>ARC-002</t>
+  </si>
+  <si>
+    <t>Hạn chế file render UI quá dài</t>
+  </si>
+  <si>
+    <t>Dễ scale</t>
+  </si>
+  <si>
+    <t>ARC-003</t>
+  </si>
+  <si>
+    <t>Áp dụng Pages/Components/Layout Architecture</t>
+  </si>
+  <si>
+    <t>Chuẩn hóa codebase</t>
+  </si>
+  <si>
+    <t>Podcast Learning System</t>
+  </si>
+  <si>
+    <t>Podcast</t>
+  </si>
+  <si>
+    <t>Hiển thị danh sách podcast shows từ DB sau khi login</t>
+  </si>
+  <si>
+    <t>Cho phép nhập RSS URL khi show chưa tồn tại</t>
+  </si>
+  <si>
+    <t>Linh hoạt nội dung</t>
+  </si>
+  <si>
+    <t>Dễ chọn bài học</t>
+  </si>
+  <si>
+    <t>Learner chọn episode để học</t>
+  </si>
+  <si>
+    <t>Trải nghiệm học tự nhiên</t>
+  </si>
+  <si>
+    <t>Embedded Audio Player</t>
+  </si>
+  <si>
+    <t>Trải nghiệm nghe liền mạch</t>
+  </si>
+  <si>
+    <t>Hiển thị transcript khi nghe</t>
+  </si>
+  <si>
+    <t>Hỗ trợ nghe hiểu</t>
+  </si>
+  <si>
+    <t>Highlight transcript theo từng câu khi audio phát</t>
+  </si>
+  <si>
+    <t>Tăng hiệu quả học</t>
+  </si>
+  <si>
+    <t>Click transcript để jump tới audio timestamp</t>
+  </si>
+  <si>
+    <t>Học tập chủ động</t>
+  </si>
+  <si>
+    <t>Biết độ khó bài học</t>
+  </si>
+  <si>
+    <t>CEFR Difficulty Classification (A1-C2)</t>
+  </si>
+  <si>
+    <t>Chọn đúng trình độ</t>
+  </si>
+  <si>
+    <t>Vocabulary Extraction từ transcript</t>
+  </si>
+  <si>
+    <t>Học từ vựng hiệu quả</t>
+  </si>
+  <si>
+    <t>Smart Flashcard Generation</t>
+  </si>
+  <si>
+    <t>Tự động tạo flashcard</t>
+  </si>
+  <si>
+    <t>Learning Analytics &amp; Dashboard</t>
+  </si>
+  <si>
+    <t>Lưu lịch sử học tập</t>
+  </si>
+  <si>
+    <t>Tổng quan kết quả</t>
+  </si>
+  <si>
+    <t>Learning Progress Tracking</t>
+  </si>
+  <si>
+    <t>Theo dõi cải thiện</t>
+  </si>
+  <si>
+    <t>Learning Time Analytics</t>
+  </si>
+  <si>
+    <t>Theo dõi thời lượng học</t>
+  </si>
+  <si>
+    <t>Listening Analytics</t>
+  </si>
+  <si>
+    <t>Assessment &amp; Learning Path</t>
+  </si>
+  <si>
+    <t>Đánh giá đầu vào</t>
+  </si>
+  <si>
+    <t>Đánh giá nghe</t>
+  </si>
+  <si>
+    <t>Đánh giá vốn từ</t>
+  </si>
+  <si>
+    <t>CEFR Score Prediction</t>
+  </si>
+  <si>
+    <t>Xác định trình độ</t>
+  </si>
+  <si>
+    <t>Learning Path</t>
+  </si>
+  <si>
+    <t>AI Learning Roadmap Generator</t>
+  </si>
+  <si>
+    <t>Có lộ trình học</t>
+  </si>
+  <si>
+    <t>Biết học gì tiếp theo</t>
+  </si>
+  <si>
+    <t>Personalized Content Recommendation</t>
+  </si>
+  <si>
+    <t>Cá nhân hóa học tập</t>
+  </si>
+  <si>
+    <t>Trực quan hóa tiến bộ</t>
+  </si>
+  <si>
+    <t>Cạnh tranh tích cực</t>
+  </si>
+  <si>
+    <t>Detailed Pronunciation Analysis</t>
+  </si>
+  <si>
+    <t>Phân tích lỗi phát âm</t>
+  </si>
+  <si>
+    <t>Hội thoại tình huống</t>
+  </si>
+  <si>
+    <t>AI Conversation Partner</t>
+  </si>
+  <si>
+    <t>Luyện giao tiếp</t>
+  </si>
+  <si>
+    <t>Sửa bài viết</t>
+  </si>
+  <si>
+    <t>Luyện đọc hiểu</t>
+  </si>
+  <si>
+    <t>Học từ vựng</t>
+  </si>
+  <si>
+    <t>Spaced Repetition System (SRS)</t>
+  </si>
+  <si>
+    <t>Ghi nhớ lâu dài</t>
+  </si>
+  <si>
+    <t>Offline</t>
+  </si>
+  <si>
+    <t>Học offline</t>
+  </si>
+  <si>
+    <t>Ôn tập offline</t>
+  </si>
+  <si>
+    <t>Sync Progress khi online lại</t>
+  </si>
+  <si>
+    <t>Đồng bộ dữ liệu</t>
+  </si>
+  <si>
+    <t>Product Roadmap (1 Founder + AI)</t>
+  </si>
+  <si>
+    <t>Phase</t>
+  </si>
+  <si>
+    <t>Deliverables</t>
+  </si>
+  <si>
+    <t>06/2026 - 07/2026</t>
+  </si>
+  <si>
+    <t>Hoàn thiện trải nghiệm học Podcast</t>
+  </si>
+  <si>
+    <t>UI Refactor, Podcast Library, Episode Browser, Embedded Audio, Transcript Viewer, Transcript Highlight, Learning History</t>
+  </si>
+  <si>
+    <t>P1 - Product Market Fit</t>
+  </si>
+  <si>
+    <t>08/2026 - 10/2026</t>
+  </si>
+  <si>
+    <t>Tăng retention &amp; cá nhân hóa</t>
+  </si>
+  <si>
+    <t>Placement Test, Learning Path, Streak, XP, Leaderboard, Analytics, Difficulty Assessment, Vocabulary Extraction, Flashcards, Pronunciation Scoring</t>
+  </si>
+  <si>
+    <t>11/2026 - 02/2027</t>
+  </si>
+  <si>
+    <t>Trở thành AI English Coach</t>
+  </si>
+  <si>
+    <t>AI Conversation, Roleplay, Writing Correction, Reading Quiz, Vocabulary Builder, SRS, Pronunciation Analysis</t>
+  </si>
+  <si>
+    <t>03/2027 - 05/2027</t>
+  </si>
+  <si>
+    <t>Bắt đầu monetize</t>
+  </si>
+  <si>
+    <t>Premium Analytics, Premium Speaking, Premium Writing, Offline Mode, Full Podcast Library</t>
+  </si>
+  <si>
+    <t>Mở rộng sang IELTS</t>
+  </si>
+  <si>
+    <t>IELTS Listening, Reading, Writing, Speaking, AI Examiner</t>
+  </si>
+  <si>
+    <t>Mở rộng B2B</t>
+  </si>
+  <si>
+    <t>Teacher Dashboard, Class Management, Student Reports</t>
+  </si>
+  <si>
+    <t>06/2028 - 11/2028</t>
+  </si>
+  <si>
+    <t>Mở rộng ngôn ngữ</t>
+  </si>
+  <si>
+    <t>Listening, Speaking, Reading, Writing cho HSK</t>
+  </si>
+  <si>
+    <t>P7 - HSK 4-6 (Optional)</t>
+  </si>
+  <si>
+    <t>12/2028 - 05/2029</t>
+  </si>
+  <si>
+    <t>HSK nâng cao</t>
+  </si>
+  <si>
+    <t>HSK Advanced</t>
+  </si>
+  <si>
+    <t>P8 - K12 Education</t>
+  </si>
+  <si>
+    <t>06/2029+</t>
+  </si>
+  <si>
+    <t>AI Learning Platform</t>
+  </si>
+  <si>
+    <t>Toán, KHTN, Tiếng Anh SGK, AI Tutor, Quiz System</t>
   </si>
 </sst>
 </file>
@@ -1526,7 +2336,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1536,6 +2346,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1552,7 +2368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1607,6 +2423,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1913,7 +2737,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>3</v>
@@ -1936,7 +2760,7 @@
         <v>8</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="E4" s="3" t="s">
         <v>9</v>
@@ -1959,7 +2783,7 @@
         <v>14</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>15</v>
@@ -1982,7 +2806,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>21</v>
@@ -2005,7 +2829,7 @@
         <v>25</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>26</v>
@@ -2028,7 +2852,7 @@
         <v>31</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>32</v>
@@ -2051,7 +2875,7 @@
         <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>38</v>
@@ -2074,7 +2898,7 @@
         <v>43</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>44</v>
@@ -2097,7 +2921,7 @@
         <v>49</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>50</v>
@@ -2120,7 +2944,7 @@
         <v>55</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>56</v>
@@ -2470,95 +3294,95 @@
   <sheetData>
     <row r="1" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B3" s="15" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B4" s="16" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B5" s="16" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>202</v>
+        <v>182</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B7" s="16" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>203</v>
+        <v>183</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B8" s="16" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>204</v>
+        <v>184</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" s="16" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>205</v>
+        <v>185</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B10" s="16" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="C10" s="16" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -2566,7 +3390,7 @@
         <v>2028</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="D11" s="16" t="s">
         <v>104</v>
@@ -2574,15 +3398,15 @@
     </row>
     <row r="14" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B16" s="13" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
@@ -2590,7 +3414,7 @@
         <v>46235</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
@@ -2598,7 +3422,7 @@
         <v>46327</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
@@ -2606,7 +3430,7 @@
         <v>46388</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -2614,7 +3438,7 @@
         <v>46508</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
@@ -2622,7 +3446,7 @@
         <v>46600</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
@@ -2630,99 +3454,99 @@
         <v>46692</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>177</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B23" s="15" t="s">
-        <v>178</v>
+        <v>158</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>179</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B24" s="15" t="s">
-        <v>180</v>
+        <v>160</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>181</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="23.5" x14ac:dyDescent="0.35">
       <c r="A27" s="1" t="s">
-        <v>182</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B29" s="13" t="s">
-        <v>183</v>
+        <v>163</v>
       </c>
       <c r="C29" s="13" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="13" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B30" s="15" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="C30" s="18">
         <v>46174</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B31" s="15" t="s">
-        <v>187</v>
+        <v>167</v>
       </c>
       <c r="C31" s="18">
         <v>46204</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>188</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B32" s="15" t="s">
-        <v>189</v>
+        <v>169</v>
       </c>
       <c r="C32" s="18">
         <v>46235</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>190</v>
+        <v>170</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B33" s="15" t="s">
-        <v>191</v>
+        <v>171</v>
       </c>
       <c r="C33" s="18">
         <v>46266</v>
       </c>
       <c r="D33" s="16" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B34" s="15" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
       <c r="C34" s="18">
         <v>46327</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
-        <v>194</v>
+        <v>174</v>
       </c>
       <c r="C35" s="18">
         <v>46388</v>
@@ -2733,29 +3557,29 @@
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B36" s="15" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="C36" s="18">
         <v>46508</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B37" s="15" t="s">
-        <v>197</v>
+        <v>177</v>
       </c>
       <c r="C37" s="18">
         <v>46692</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B38" s="15" t="s">
-        <v>199</v>
+        <v>179</v>
       </c>
       <c r="C38" s="16">
         <v>2028</v>
@@ -2788,7 +3612,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="31" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -2801,1541 +3625,1541 @@
       <c r="K1" s="14"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
       <c r="J2" s="14"/>
       <c r="K2" s="14"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B3" s="13" t="s">
-        <v>281</v>
+        <v>261</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>282</v>
+        <v>262</v>
       </c>
       <c r="D3" s="13" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>284</v>
+        <v>264</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>285</v>
+        <v>265</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>286</v>
+        <v>266</v>
       </c>
       <c r="H3" s="13" t="s">
-        <v>287</v>
+        <v>267</v>
       </c>
       <c r="I3" s="13" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="K3" s="13" t="s">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="L3" s="13" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B4" s="16" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>293</v>
+        <v>273</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>294</v>
+        <v>274</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H4" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I4" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J4" s="16" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="K4" s="16" t="s">
-        <v>300</v>
+        <v>280</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B5" s="16" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>303</v>
+        <v>283</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G5" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I5" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J5" s="16" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="K5" s="16" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B6" s="16" t="s">
-        <v>305</v>
+        <v>285</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>307</v>
+        <v>287</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I6" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J6" s="16" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="K6" s="16" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B7" s="16" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="C7" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="D7" s="16" t="s">
-        <v>310</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>312</v>
-      </c>
       <c r="H7" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I7" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>313</v>
+        <v>293</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B8" s="16" t="s">
-        <v>314</v>
+        <v>294</v>
       </c>
       <c r="C8" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>316</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G8" s="16" t="s">
-        <v>312</v>
-      </c>
       <c r="H8" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="I8" s="16" t="s">
+        <v>278</v>
+      </c>
+      <c r="J8" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="K8" s="16" t="s">
         <v>297</v>
-      </c>
-      <c r="I8" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="J8" s="16" t="s">
-        <v>299</v>
-      </c>
-      <c r="K8" s="16" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B9" s="16" t="s">
-        <v>318</v>
+        <v>298</v>
       </c>
       <c r="C9" s="16" t="s">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>319</v>
+        <v>299</v>
       </c>
       <c r="E9" s="16" t="s">
-        <v>320</v>
+        <v>300</v>
       </c>
       <c r="F9" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G9" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I9" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>291</v>
+        <v>271</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>321</v>
+        <v>301</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B10" s="16" t="s">
-        <v>322</v>
+        <v>302</v>
       </c>
       <c r="C10" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>303</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="G10" s="16" t="s">
         <v>292</v>
       </c>
-      <c r="D10" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="F10" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G10" s="16" t="s">
-        <v>312</v>
-      </c>
       <c r="H10" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I10" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J10" s="16" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="K10" s="16" t="s">
-        <v>325</v>
+        <v>305</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B11" s="16" t="s">
-        <v>326</v>
+        <v>306</v>
       </c>
       <c r="C11" s="16" t="s">
-        <v>327</v>
+        <v>307</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>328</v>
+        <v>308</v>
       </c>
       <c r="E11" s="16" t="s">
-        <v>329</v>
+        <v>309</v>
       </c>
       <c r="F11" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G11" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I11" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J11" s="16" t="s">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>330</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B12" s="16" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>333</v>
+        <v>313</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>334</v>
+        <v>314</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G12" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H12" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J12" s="16" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="K12" s="16" t="s">
-        <v>336</v>
+        <v>316</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B13" s="16" t="s">
-        <v>337</v>
+        <v>317</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>338</v>
+        <v>318</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>339</v>
+        <v>319</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G13" s="16" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="H13" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J13" s="16" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="K13" s="16" t="s">
-        <v>340</v>
+        <v>320</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B14" s="16" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>342</v>
+        <v>322</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>343</v>
+        <v>323</v>
       </c>
       <c r="F14" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J14" s="16" t="s">
-        <v>331</v>
+        <v>311</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>344</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B15" s="16" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H15" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>341</v>
+        <v>321</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="B16" s="16" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="C16" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>330</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="G16" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="D16" s="16" t="s">
-        <v>350</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>351</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>352</v>
-      </c>
       <c r="H16" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J16" s="16" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>353</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B17" s="16" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="C17" s="16" t="s">
+        <v>312</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="F17" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="G17" s="16" t="s">
         <v>332</v>
       </c>
-      <c r="D17" s="16" t="s">
-        <v>355</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="F17" s="16" t="s">
-        <v>295</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>352</v>
-      </c>
       <c r="H17" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I17" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J17" s="16" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>357</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B18" s="16" t="s">
-        <v>358</v>
+        <v>338</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>332</v>
+        <v>312</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>359</v>
+        <v>339</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>360</v>
+        <v>340</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="G18" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H18" s="16" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J18" s="16" t="s">
-        <v>354</v>
+        <v>334</v>
       </c>
       <c r="K18" s="16" t="s">
-        <v>363</v>
+        <v>343</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B19" s="16" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>366</v>
+        <v>346</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>367</v>
+        <v>347</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G19" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H19" s="16" t="s">
-        <v>297</v>
+        <v>277</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="K19" s="16"/>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B20" s="16" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>371</v>
+        <v>351</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="G20" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="K20" s="16"/>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B21" s="16" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>373</v>
+        <v>353</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>374</v>
+        <v>354</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="G21" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J21" s="16" t="s">
-        <v>369</v>
+        <v>349</v>
       </c>
       <c r="K21" s="16"/>
     </row>
     <row r="22" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B22" s="16" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>376</v>
+        <v>356</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>377</v>
+        <v>357</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="G22" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J22" s="16" t="s">
-        <v>364</v>
+        <v>344</v>
       </c>
       <c r="K22" s="16"/>
     </row>
     <row r="23" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B23" s="16" t="s">
-        <v>378</v>
+        <v>358</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>379</v>
+        <v>359</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>380</v>
+        <v>360</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="G23" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J23" s="16" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="K23" s="16"/>
     </row>
     <row r="24" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B24" s="16" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>383</v>
+        <v>363</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J24" s="16" t="s">
-        <v>375</v>
+        <v>355</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B25" s="16" t="s">
-        <v>384</v>
+        <v>364</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>386</v>
+        <v>366</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>387</v>
+        <v>367</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>361</v>
+        <v>341</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>362</v>
+        <v>342</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J25" s="16" t="s">
-        <v>388</v>
+        <v>368</v>
       </c>
       <c r="K25" s="16"/>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B26" s="16" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>390</v>
+        <v>370</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>391</v>
+        <v>371</v>
       </c>
       <c r="F26" s="16" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="G26" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H26" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J26" s="16" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="K26" s="16"/>
     </row>
     <row r="27" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B27" s="16" t="s">
-        <v>395</v>
+        <v>375</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="F27" s="16" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="G27" s="16" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="H27" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J27" s="16" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="K27" s="16"/>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B28" s="16" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="G28" s="16" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="H28" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J28" s="16" t="s">
-        <v>394</v>
+        <v>374</v>
       </c>
       <c r="K28" s="16"/>
     </row>
     <row r="29" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B29" s="16" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>403</v>
+        <v>383</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>392</v>
+        <v>372</v>
       </c>
       <c r="G29" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H29" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J29" s="16" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="K29" s="16"/>
     </row>
     <row r="30" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B30" s="16" t="s">
-        <v>405</v>
+        <v>385</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="D30" s="16" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="G30" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H30" s="16" t="s">
         <v>82</v>
       </c>
       <c r="I30" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J30" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="K30" s="16"/>
     </row>
     <row r="31" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B31" s="16" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="D31" s="16" t="s">
-        <v>411</v>
+        <v>391</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="G31" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H31" s="16" t="s">
         <v>82</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J31" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="K31" s="16"/>
     </row>
     <row r="32" spans="2:11" x14ac:dyDescent="0.35">
       <c r="B32" s="16" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="D32" s="16" t="s">
-        <v>413</v>
+        <v>393</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="G32" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H32" s="16" t="s">
         <v>82</v>
       </c>
       <c r="I32" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J32" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="K32" s="16"/>
     </row>
     <row r="33" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B33" s="16" t="s">
-        <v>414</v>
+        <v>394</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="D33" s="16" t="s">
         <v>92</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>408</v>
+        <v>388</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="G33" s="16" t="s">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="H33" s="16" t="s">
         <v>82</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J33" s="16" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="K33" s="16"/>
     </row>
     <row r="34" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B34" s="16" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="C34" s="16" t="s">
         <v>102</v>
       </c>
       <c r="D34" s="16" t="s">
-        <v>417</v>
+        <v>397</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="G34" s="16" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="H34" s="16" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J34" s="16" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="K34" s="16"/>
       <c r="L34" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="35" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B35" s="16" t="s">
-        <v>421</v>
+        <v>401</v>
       </c>
       <c r="C35" s="16" t="s">
         <v>102</v>
       </c>
       <c r="D35" s="16" t="s">
-        <v>422</v>
+        <v>402</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="G35" s="16" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J35" s="16" t="s">
-        <v>423</v>
+        <v>403</v>
       </c>
       <c r="K35" s="16"/>
       <c r="L35" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="36" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B36" s="16" t="s">
-        <v>424</v>
+        <v>404</v>
       </c>
       <c r="C36" s="16" t="s">
         <v>102</v>
       </c>
       <c r="D36" s="16" t="s">
-        <v>425</v>
+        <v>405</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="F36" s="16" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="G36" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H36" s="16" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J36" s="16" t="s">
-        <v>426</v>
+        <v>406</v>
       </c>
       <c r="K36" s="16"/>
       <c r="L36" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B37" s="16" t="s">
-        <v>427</v>
+        <v>407</v>
       </c>
       <c r="C37" s="16" t="s">
         <v>102</v>
       </c>
       <c r="D37" s="16" t="s">
-        <v>428</v>
+        <v>408</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>418</v>
+        <v>398</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J37" s="16" t="s">
-        <v>429</v>
+        <v>409</v>
       </c>
       <c r="K37" s="16"/>
       <c r="L37" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="38" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B38" s="16" t="s">
-        <v>430</v>
+        <v>410</v>
       </c>
       <c r="C38" s="16" t="s">
         <v>102</v>
       </c>
       <c r="D38" s="16" t="s">
-        <v>431</v>
+        <v>411</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>432</v>
+        <v>412</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>419</v>
+        <v>399</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>196</v>
+        <v>176</v>
       </c>
       <c r="I38" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J38" s="16" t="s">
-        <v>433</v>
+        <v>413</v>
       </c>
       <c r="K38" s="16"/>
       <c r="L38" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="39" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B39" s="16" t="s">
-        <v>434</v>
+        <v>414</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="D39" s="16" t="s">
         <v>96</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="G39" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H39" s="16" t="s">
         <v>95</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J39" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="K39" s="16"/>
       <c r="L39" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="40" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B40" s="16" t="s">
-        <v>438</v>
+        <v>418</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="D40" s="16" t="s">
         <v>97</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>436</v>
+        <v>416</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="G40" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H40" s="16" t="s">
         <v>95</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J40" s="16" t="s">
-        <v>439</v>
+        <v>419</v>
       </c>
       <c r="K40" s="16"/>
       <c r="L40" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="41" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B41" s="16" t="s">
-        <v>440</v>
+        <v>420</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>435</v>
+        <v>415</v>
       </c>
       <c r="D41" s="16" t="s">
-        <v>441</v>
+        <v>421</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>437</v>
+        <v>417</v>
       </c>
       <c r="G41" s="16" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="H41" s="16" t="s">
         <v>95</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J41" s="16" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="K41" s="16"/>
       <c r="L41" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="42" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B42" s="16" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D42" s="16" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="G42" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H42" s="16" t="s">
         <v>103</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J42" s="16" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="K42" s="16"/>
       <c r="L42" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="43" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B43" s="16" t="s">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D43" s="16" t="s">
-        <v>449</v>
+        <v>429</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="G43" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H43" s="16" t="s">
         <v>103</v>
       </c>
       <c r="I43" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J43" s="16" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="K43" s="16"/>
       <c r="L43" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="44" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B44" s="16" t="s">
-        <v>450</v>
+        <v>430</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D44" s="16" t="s">
-        <v>451</v>
+        <v>431</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="G44" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H44" s="16" t="s">
         <v>103</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J44" s="16" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="K44" s="16"/>
       <c r="L44" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="45" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B45" s="16" t="s">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>198</v>
+        <v>178</v>
       </c>
       <c r="D45" s="16" t="s">
-        <v>453</v>
+        <v>433</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="H45" s="16" t="s">
         <v>103</v>
       </c>
       <c r="I45" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J45" s="16" t="s">
-        <v>447</v>
+        <v>427</v>
       </c>
       <c r="K45" s="16"/>
       <c r="L45" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="46" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B46" s="16" t="s">
-        <v>454</v>
+        <v>434</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>456</v>
+        <v>436</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H46" s="16" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="I46" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J46" s="16" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="K46" s="16"/>
       <c r="L46" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B47" s="16" t="s">
-        <v>461</v>
+        <v>441</v>
       </c>
       <c r="C47" s="16" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>462</v>
+        <v>442</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="G47" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H47" s="16" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="I47" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J47" s="16" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="K47" s="16"/>
       <c r="L47" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="48" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B48" s="16" t="s">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="G48" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H48" s="16" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="I48" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J48" s="16" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="K48" s="16"/>
       <c r="L48" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="49" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B49" s="16" t="s">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>466</v>
+        <v>446</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>393</v>
+        <v>373</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="I49" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J49" s="16" t="s">
-        <v>385</v>
+        <v>365</v>
       </c>
       <c r="K49" s="16"/>
       <c r="L49" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50" spans="2:12" x14ac:dyDescent="0.35">
       <c r="B50" s="16" t="s">
-        <v>467</v>
+        <v>447</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>468</v>
+        <v>448</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>469</v>
+        <v>449</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="H50" s="16" t="s">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="I50" s="16" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="J50" s="16" t="s">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="K50" s="16"/>
       <c r="L50" s="16" t="s">
-        <v>470</v>
+        <v>450</v>
       </c>
     </row>
   </sheetData>
@@ -4344,6 +5168,3188 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L173"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="8.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.08984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.6328125" style="23" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="36.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="31" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>606</v>
+      </c>
+      <c r="J1" s="20"/>
+      <c r="K1" s="14"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J2" s="20"/>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B3" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J4" s="22"/>
+      <c r="K4" s="16"/>
+    </row>
+    <row r="5" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J5" s="22"/>
+      <c r="K5" s="16"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J6" s="22"/>
+      <c r="K6" s="16"/>
+    </row>
+    <row r="7" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J7" s="22"/>
+      <c r="K7" s="16"/>
+    </row>
+    <row r="8" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J8" s="22"/>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B9" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J9" s="22"/>
+      <c r="K9" s="16"/>
+    </row>
+    <row r="10" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B10" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J10" s="22"/>
+      <c r="K10" s="16"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B11" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J11" s="22"/>
+      <c r="K11" s="16"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J12" s="22"/>
+      <c r="K12" s="16"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B13" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J13" s="22"/>
+      <c r="K13" s="16"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B14" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J14" s="22"/>
+      <c r="K14" s="16"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B15" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J15" s="22"/>
+      <c r="K15" s="16"/>
+    </row>
+    <row r="16" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B16" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J16" s="22"/>
+      <c r="K16" s="16"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="22"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J18" s="22"/>
+      <c r="K18" s="16"/>
+    </row>
+    <row r="19" spans="1:11" ht="31" x14ac:dyDescent="0.35">
+      <c r="A19" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="J19" s="22"/>
+      <c r="K19" s="16"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="J20" s="22"/>
+      <c r="K20" s="16"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B21" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J21" s="22"/>
+      <c r="K21" s="16"/>
+    </row>
+    <row r="22" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="B22" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J22" s="22"/>
+      <c r="K22" s="16"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B23" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J23" s="22"/>
+      <c r="K23" s="16"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B24" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J24" s="22"/>
+      <c r="K24" s="16"/>
+    </row>
+    <row r="25" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="B25" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J25" s="22"/>
+      <c r="K25" s="16"/>
+    </row>
+    <row r="26" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+      <c r="B26" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J26" s="22"/>
+      <c r="K26" s="16"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B27" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J27" s="22"/>
+      <c r="K27" s="16"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B28" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J28" s="22"/>
+      <c r="K28" s="16"/>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B29" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J29" s="22"/>
+      <c r="K29" s="16"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B30" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J30" s="22"/>
+      <c r="K30" s="16"/>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B31" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J31" s="22"/>
+      <c r="K31" s="16"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B32" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J32" s="22"/>
+      <c r="K32" s="16"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B33" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J33" s="22"/>
+      <c r="K33" s="16"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J34" s="22"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J35" s="22"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+    </row>
+    <row r="36" spans="1:12" ht="31" x14ac:dyDescent="0.35">
+      <c r="A36" s="19" t="s">
+        <v>657</v>
+      </c>
+      <c r="J36" s="22"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J37" s="22"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B38" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J38" s="22"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J39" s="22"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B40" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J40" s="22"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B41" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J41" s="22"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B42" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J42" s="22"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B43" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J43" s="22"/>
+      <c r="K43" s="16"/>
+      <c r="L43" s="16"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B44" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J44" s="22"/>
+      <c r="K44" s="16"/>
+      <c r="L44" s="16"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J45" s="22"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J46" s="22"/>
+      <c r="K46" s="16"/>
+      <c r="L46" s="16"/>
+    </row>
+    <row r="47" spans="1:12" ht="31" x14ac:dyDescent="0.35">
+      <c r="A47" s="19" t="s">
+        <v>665</v>
+      </c>
+      <c r="J47" s="22"/>
+      <c r="K47" s="16"/>
+      <c r="L47" s="16"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="J48" s="22"/>
+      <c r="K48" s="16"/>
+      <c r="L48" s="16"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B49" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J49" s="22"/>
+      <c r="K49" s="16"/>
+      <c r="L49" s="16"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B50" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J50" s="22"/>
+      <c r="K50" s="16"/>
+      <c r="L50" s="16"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B51" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B52" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B53" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B54" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B55" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B56" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" ht="31" x14ac:dyDescent="0.35">
+      <c r="A59" s="19" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="B61" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B62" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B63" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E63" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" ht="29" x14ac:dyDescent="0.35">
+      <c r="B64" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B65" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B66" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B67" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="31" x14ac:dyDescent="0.35">
+      <c r="A70" s="19" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B72" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B73" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E73" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B74" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B75" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B76" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B77" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B78" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E78" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B79" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="31" x14ac:dyDescent="0.35">
+      <c r="A82" s="19" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B84" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B85" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B86" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B87" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B88" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="31" x14ac:dyDescent="0.35">
+      <c r="A91" s="19" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B93" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E93" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B94" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B95" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E95" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B96" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B97" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" s="23" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B101" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B102" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="E102" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B103" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="E103" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B104" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="E104" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B105" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E105" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B106" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="E106" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" ht="31" x14ac:dyDescent="0.35">
+      <c r="A109" s="19" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="B111" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="29" x14ac:dyDescent="0.35">
+      <c r="B112" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="E112" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B113" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="E113" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B114" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="E114" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B115" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="E115" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B116" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="E116" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A119" s="19" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B121" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H121" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B122" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B123" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="E123" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B124" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B125" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="E125" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A128" s="19" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B130" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H130" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B131" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="E131" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B132" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="E132" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B133" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="E133" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B134" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="E134" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B135" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="E135" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B136" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="E136" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A139" s="19" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B141" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B142" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E142" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B143" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="E143" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B144" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="E144" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B145" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="E145" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A148" s="19" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B150" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B151" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="E151" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B152" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E152" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B153" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="E153" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B154" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="E154" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+      <c r="B155" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="E155" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A158" s="19" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B160" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B161" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E161" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B162" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E162" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B163" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E163" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B164" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="E164" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" ht="31" x14ac:dyDescent="0.35">
+      <c r="A167" s="19" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B169" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B170" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="E170" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B171" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="E171" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B172" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="E172" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="B173" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="E173" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:10" ht="31" x14ac:dyDescent="0.35">
+      <c r="A1" s="19" t="s">
+        <v>694</v>
+      </c>
+      <c r="J1" s="23"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J2" s="23"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="B3" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="J3" s="23"/>
+    </row>
+    <row r="4" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="B4" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="J4" s="23"/>
+    </row>
+    <row r="5" spans="1:10" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="J5" s="23"/>
+    </row>
+    <row r="6" spans="1:10" ht="87" x14ac:dyDescent="0.35">
+      <c r="B6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="J6" s="23"/>
+    </row>
+    <row r="7" spans="1:10" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="J7" s="23"/>
+    </row>
+    <row r="8" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="J8" s="23"/>
+    </row>
+    <row r="9" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="J9" s="23"/>
+    </row>
+    <row r="10" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="J10" s="23"/>
+    </row>
+    <row r="11" spans="1:10" ht="58" x14ac:dyDescent="0.35">
+      <c r="B11" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="J11" s="23"/>
+    </row>
+    <row r="12" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B12" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>723</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>724</v>
+      </c>
+      <c r="J12" s="23"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C126"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -4356,51 +8362,51 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C1" s="13" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="15" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="B2" s="16" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="C2" s="16" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" s="15" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="B3" s="16" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="C3" s="16" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" s="15" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B4" s="16" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="23.5" x14ac:dyDescent="0.35">
       <c r="B6" s="1" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="C6"/>
     </row>
@@ -4410,7 +8416,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="C8"/>
     </row>
@@ -4420,13 +8426,13 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B10" s="6" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="C10"/>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B11" s="6" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="C11"/>
     </row>
@@ -4436,7 +8442,7 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="C13"/>
     </row>
@@ -4446,7 +8452,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="C15"/>
     </row>
@@ -4456,7 +8462,7 @@
     </row>
     <row r="17" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="C17"/>
     </row>
@@ -4466,13 +8472,13 @@
     </row>
     <row r="19" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B19" s="6" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C19"/>
     </row>
     <row r="20" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B20" s="6" t="s">
-        <v>215</v>
+        <v>195</v>
       </c>
       <c r="C20"/>
     </row>
@@ -4482,7 +8488,7 @@
     </row>
     <row r="22" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="C22"/>
     </row>
@@ -4500,7 +8506,7 @@
     </row>
     <row r="26" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="C26"/>
     </row>
@@ -4510,7 +8516,7 @@
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="C28"/>
     </row>
@@ -4520,7 +8526,7 @@
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="C30"/>
     </row>
@@ -4530,15 +8536,15 @@
     </row>
     <row r="32" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B32" s="2" t="s">
-        <v>219</v>
+        <v>199</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>220</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B33" s="3" t="s">
-        <v>221</v>
+        <v>201</v>
       </c>
       <c r="C33" s="3">
         <v>120</v>
@@ -4546,7 +8552,7 @@
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B34" s="3" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="C34" s="3">
         <v>110</v>
@@ -4554,7 +8560,7 @@
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B35" s="3" t="s">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="C35" s="3">
         <v>95</v>
@@ -4562,7 +8568,7 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B36" s="3" t="s">
-        <v>224</v>
+        <v>204</v>
       </c>
       <c r="C36" s="3">
         <v>130</v>
@@ -4574,7 +8580,7 @@
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>225</v>
+        <v>205</v>
       </c>
       <c r="C38"/>
     </row>
@@ -4584,7 +8590,7 @@
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="C40"/>
     </row>
@@ -4594,19 +8600,19 @@
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B42" s="6" t="s">
-        <v>227</v>
+        <v>207</v>
       </c>
       <c r="C42"/>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B43" s="6" t="s">
-        <v>228</v>
+        <v>208</v>
       </c>
       <c r="C43"/>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B44" s="6" t="s">
-        <v>229</v>
+        <v>209</v>
       </c>
       <c r="C44"/>
     </row>
@@ -4624,7 +8630,7 @@
     </row>
     <row r="48" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
       <c r="B48" s="1" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="C48"/>
     </row>
@@ -4634,7 +8640,7 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="C50"/>
     </row>
@@ -4644,7 +8650,7 @@
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>232</v>
+        <v>212</v>
       </c>
       <c r="C52"/>
     </row>
@@ -4654,7 +8660,7 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>233</v>
+        <v>213</v>
       </c>
       <c r="C54"/>
     </row>
@@ -4664,7 +8670,7 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B56" s="6" t="s">
-        <v>234</v>
+        <v>214</v>
       </c>
       <c r="C56"/>
     </row>
@@ -4674,7 +8680,7 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="C58"/>
     </row>
@@ -4684,7 +8690,7 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B60" s="6" t="s">
-        <v>236</v>
+        <v>216</v>
       </c>
       <c r="C60"/>
     </row>
@@ -4694,7 +8700,7 @@
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="C62"/>
     </row>
@@ -4704,7 +8710,7 @@
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>238</v>
+        <v>218</v>
       </c>
       <c r="C64"/>
     </row>
@@ -4714,7 +8720,7 @@
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="C66"/>
     </row>
@@ -4732,7 +8738,7 @@
     </row>
     <row r="70" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
       <c r="B70" s="1" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="C70"/>
     </row>
@@ -4742,50 +8748,50 @@
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B72" s="2" t="s">
-        <v>241</v>
+        <v>221</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>242</v>
+        <v>222</v>
       </c>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B73" s="3" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B74" s="3" t="s">
-        <v>245</v>
+        <v>225</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>246</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B75" s="3" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B76" s="3" t="s">
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>250</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B77" s="3" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.35">
@@ -4794,7 +8800,7 @@
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="C79"/>
     </row>
@@ -4804,13 +8810,13 @@
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B81" s="6" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="C81"/>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B82" s="6" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="C82"/>
     </row>
@@ -4828,7 +8834,7 @@
     </row>
     <row r="86" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
       <c r="B86" s="1" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="C86"/>
     </row>
@@ -4838,7 +8844,7 @@
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="C88"/>
     </row>
@@ -4848,19 +8854,19 @@
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B90" s="6" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="C90"/>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B91" s="6" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="C91"/>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B92" s="6" t="s">
-        <v>259</v>
+        <v>239</v>
       </c>
       <c r="C92"/>
     </row>
@@ -4870,7 +8876,7 @@
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B94" t="s">
-        <v>260</v>
+        <v>240</v>
       </c>
       <c r="C94"/>
     </row>
@@ -4880,7 +8886,7 @@
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B96" t="s">
-        <v>261</v>
+        <v>241</v>
       </c>
       <c r="C96"/>
     </row>
@@ -4890,19 +8896,19 @@
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B98" s="6" t="s">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="C98"/>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B99" s="6" t="s">
-        <v>263</v>
+        <v>243</v>
       </c>
       <c r="C99"/>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B100" s="6" t="s">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="C100"/>
     </row>
@@ -4912,7 +8918,7 @@
     </row>
     <row r="102" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="C102"/>
     </row>
@@ -4930,7 +8936,7 @@
     </row>
     <row r="106" spans="2:3" ht="23.5" x14ac:dyDescent="0.35">
       <c r="B106" s="1" t="s">
-        <v>266</v>
+        <v>246</v>
       </c>
       <c r="C106"/>
     </row>
@@ -4940,7 +8946,7 @@
     </row>
     <row r="108" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="C108"/>
     </row>
@@ -4950,7 +8956,7 @@
     </row>
     <row r="110" spans="2:3" ht="17.5" x14ac:dyDescent="0.35">
       <c r="B110" s="5" t="s">
-        <v>268</v>
+        <v>248</v>
       </c>
       <c r="C110"/>
     </row>
@@ -4960,7 +8966,7 @@
     </row>
     <row r="112" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
-        <v>269</v>
+        <v>249</v>
       </c>
       <c r="C112"/>
     </row>
@@ -4970,19 +8976,19 @@
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B114" s="6" t="s">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="C114"/>
     </row>
     <row r="115" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B115" s="6" t="s">
-        <v>271</v>
+        <v>251</v>
       </c>
       <c r="C115"/>
     </row>
     <row r="116" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B116" s="6" t="s">
-        <v>272</v>
+        <v>252</v>
       </c>
       <c r="C116"/>
     </row>
@@ -4992,7 +8998,7 @@
     </row>
     <row r="118" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
-        <v>273</v>
+        <v>253</v>
       </c>
       <c r="C118"/>
     </row>
@@ -5002,31 +9008,31 @@
     </row>
     <row r="120" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B120" s="9" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="C120"/>
     </row>
     <row r="121" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B121" s="9" t="s">
-        <v>275</v>
+        <v>255</v>
       </c>
       <c r="C121"/>
     </row>
     <row r="122" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B122" s="9" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="C122"/>
     </row>
     <row r="123" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B123" s="9" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C123"/>
     </row>
     <row r="124" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B124" s="9" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="C124"/>
     </row>
@@ -5036,7 +9042,7 @@
     </row>
     <row r="126" spans="2:3" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>279</v>
+        <v>259</v>
       </c>
       <c r="C126"/>
     </row>
@@ -5045,242 +9051,1312 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="27.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="11">
-        <v>46174</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="174" x14ac:dyDescent="0.35">
-      <c r="A3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="130.5" x14ac:dyDescent="0.35">
-      <c r="A6" s="4" t="s">
-        <v>30</v>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A6" s="3" t="s">
+        <v>454</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>124</v>
+        <v>455</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>456</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>32</v>
+        <v>457</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>125</v>
+        <v>341</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>34</v>
+        <v>276</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A7" s="4" t="s">
-        <v>36</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A7" s="3" t="s">
+        <v>458</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>126</v>
+        <v>455</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>459</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>127</v>
+        <v>460</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>128</v>
+        <v>341</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>40</v>
+        <v>276</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="116" x14ac:dyDescent="0.35">
-      <c r="A8" s="4" t="s">
-        <v>42</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="3" t="s">
+        <v>461</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>129</v>
+        <v>455</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>462</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>130</v>
+        <v>463</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>131</v>
+        <v>341</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>46</v>
+        <v>276</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A9" s="3" t="s">
+        <v>464</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>132</v>
+        <v>455</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>465</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>133</v>
+        <v>466</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>134</v>
+        <v>341</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>52</v>
+        <v>276</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>54</v>
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="3" t="s">
+        <v>467</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>135</v>
+        <v>455</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>468</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>136</v>
+        <v>469</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>137</v>
+        <v>372</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>58</v>
+        <v>332</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>59</v>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A13" s="19" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A15" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A16" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A17" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A20" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A23" s="19" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A25" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A27" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A28" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A32" s="19" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A34" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A35" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A36" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A37" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A38" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A40" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A43" s="19" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A45" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A46" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A47" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A49" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A52" s="19" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A54" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A57" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A58" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A59" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A62" s="19" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A64" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A65" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="E65" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="E66" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="E67" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="E68" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="31" x14ac:dyDescent="0.35">
+      <c r="A71" s="19" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B74" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="E75" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="B76" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A77" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="E77" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A82" s="5" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A83" s="6"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A84" s="6" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A85" s="6" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A86" s="6" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A87" s="6" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A88" s="6" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A89" s="6" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A90" s="6" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A91" s="6" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A93" s="5" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A94" s="6"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A95" s="6" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A96" s="6" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A97" s="6" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A98" s="6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A99" s="6" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A100" s="6" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A101" s="6" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A102" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A103" s="6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A104" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A106" s="5" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A107" s="6"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A108" s="6" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A109" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A110" s="6" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A111" s="6" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A112" s="6" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A113" s="6" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A114" s="6" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A116" s="5" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A117" s="6"/>
+    </row>
+    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A118" s="6" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A119" s="6" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A120" s="6" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A121" s="6" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A122" s="6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A124" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A125" s="6"/>
+    </row>
+    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A126" s="6" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A127" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A128" s="6" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A129" s="6" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A131" t="s">
+        <v>605</v>
       </c>
     </row>
   </sheetData>
